--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 77 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 76 clubs short</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1003,8 +1003,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3513,11 +3513,11 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>2</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>7</v>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>1</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13789,8 +13789,8 @@
       <c r="S135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U135" s="9" t="n">
         <v>0</v>
@@ -15939,7 +15939,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16104,7 +16104,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -16764,7 +16764,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 76 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 67 clubs short</t>
         </is>
       </c>
     </row>
@@ -5797,17 +5797,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6338,8 +6338,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7872,8 +7872,8 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="9" t="n">
-        <v>0</v>
+      <c r="T74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8472,8 +8472,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8648,8 +8648,8 @@
       <c r="S82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T82" s="9" t="n">
-        <v>0</v>
+      <c r="T82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U82" s="9" t="n">
         <v>0</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10412,8 +10412,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10509,8 +10509,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12158,8 +12158,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14195,8 +14195,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14513,7 +14513,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14583,8 +14583,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -16284,7 +16284,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -16302,7 +16302,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16368,7 +16368,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16401,7 +16401,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16434,7 +16434,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16533,7 +16533,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16665,7 +16665,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16797,7 +16797,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 67 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 31 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -906,8 +906,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1876,8 +1876,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2167,8 +2167,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2846,8 +2846,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3593,22 +3593,22 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -3913,8 +3913,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4398,8 +4398,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4689,8 +4689,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4980,8 +4980,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5077,8 +5077,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5174,8 +5174,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="9" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6047,8 +6047,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6144,8 +6144,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="9" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6629,8 +6629,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7308,8 +7308,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7405,8 +7405,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="9" t="n">
         <v>0</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7890,8 +7890,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8651,8 +8651,8 @@
       <c r="T82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
+      <c r="U82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V82" s="9" t="n">
         <v>0</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9151,8 +9151,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9345,8 +9345,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10121,8 +10121,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10994,8 +10994,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11285,8 +11285,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11473,8 +11473,8 @@
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="9" t="n">
-        <v>3</v>
+      <c r="X111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12449,8 +12449,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13031,8 +13031,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13904,8 +13904,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14077,8 +14077,8 @@
       <c r="R138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S138" s="9" t="n">
-        <v>1</v>
+      <c r="S138" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T138" s="10" t="n">
         <v>1</v>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14486,8 +14486,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -14674,14 +14674,14 @@
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X144" s="9" t="n">
-        <v>0</v>
+      <c r="X144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="9" t="n">
         <v>0</v>
@@ -14772,7 +14772,7 @@
         <v>0</v>
       </c>
       <c r="X145" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14971,8 +14971,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15359,8 +15359,8 @@
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15844,8 +15844,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -15939,7 +15939,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16005,7 +16005,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16071,7 +16071,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16104,7 +16104,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16137,7 +16137,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16170,7 +16170,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16236,7 +16236,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16269,7 +16269,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16335,7 +16335,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16368,7 +16368,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16434,7 +16434,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16467,7 +16467,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16566,7 +16566,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16665,7 +16665,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16731,7 +16731,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16797,7 +16797,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -16896,7 +16896,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/201/inyear.xlsx
+++ b/docs/d/201/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 31 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 31 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1864,8 +1864,8 @@
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="9" t="n">
-        <v>3</v>
+      <c r="V12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2061,8 +2061,8 @@
       <c r="V14" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W14" s="9" t="n">
-        <v>3</v>
+      <c r="W14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>6</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="10" t="n">
         <v>2</v>
@@ -3992,8 +3992,8 @@
       <c r="S34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T34" s="9" t="n">
-        <v>0</v>
+      <c r="T34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U34" s="9" t="n">
         <v>0</v>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>-14</v>
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="10" t="n">
         <v>1</v>
@@ -4875,7 +4875,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>7</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5065,8 +5065,8 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -8031,10 +8031,10 @@
         <v>6</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8639,8 +8639,8 @@
       <c r="P82" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" s="9" t="n">
-        <v>1</v>
+      <c r="Q82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
@@ -10262,10 +10262,10 @@
         <v>27</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>1</v>
@@ -10979,8 +10979,8 @@
       <c r="T106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U106" s="9" t="n">
-        <v>0</v>
+      <c r="U106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V106" s="9" t="n">
         <v>1</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X117" s="9" t="n">
         <v>3</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12225,8 +12225,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P119" s="9" t="n">
-        <v>3</v>
+      <c r="P119" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -14530,10 +14530,10 @@
         <v>18</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="L143" s="8" t="inlineStr">
         <is>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L152" s="8" t="inlineStr">
         <is>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>4</v>
       </c>
       <c r="W158" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X158" s="10" t="n">
         <v>7</v>
@@ -16296,7 +16296,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16428,7 +16428,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16527,7 +16527,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16890,7 +16890,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16956,13 +16956,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
